--- a/Excel/Role.xlsx
+++ b/Excel/Role.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\42421\Desktop\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D422719-ABAE-4CC5-8C06-2814DF3F9877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEECE51A-7595-458C-B359-DDA6B93E5314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,10 +343,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1003001,1003002,1003003,1003004,1003005,1003006,1003007,1003008,1003009,1003010,1003011,1003012,1003013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.2,0.2,0.4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -404,6 +400,10 @@
   </si>
   <si>
     <t>2005001,2005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003001,1003002,1003003,1003004,1003005,1003006,1003007,1003008,1003009,1003010,1003011,1003012</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,7 +753,7 @@
     <col min="1" max="8" width="9" style="1"/>
     <col min="9" max="11" width="9" style="2"/>
     <col min="12" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="9" style="2"/>
+    <col min="16" max="16" width="85.375" style="2" customWidth="1"/>
     <col min="17" max="19" width="9" style="1"/>
     <col min="20" max="20" width="9" style="2"/>
     <col min="21" max="22" width="9" style="1"/>
@@ -1127,19 +1127,19 @@
         <v>1003012</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>73</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S7" s="1">
         <v>1003</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -1147,10 +1147,10 @@
         <v>2001</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="G8" s="1">
         <v>0.5</v>
@@ -1171,7 +1171,7 @@
         <v>2001</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
@@ -1179,10 +1179,10 @@
         <v>2002</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="G9" s="1">
         <v>0.5</v>
@@ -1208,10 +1208,10 @@
         <v>2003</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1237,10 +1237,10 @@
         <v>2004</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1252,7 +1252,7 @@
         <v>2004001</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="1">
         <v>-1</v>
@@ -1266,10 +1266,10 @@
         <v>2005</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1278,16 +1278,16 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="Q12" s="1">
         <v>-1</v>
@@ -1296,7 +1296,7 @@
         <v>2005</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Role.xlsx
+++ b/Excel/Role.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEECE51A-7595-458C-B359-DDA6B93E5314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747261B6-5138-4EDC-A064-DDC53675FC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="104">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -404,6 +404,18 @@
   </si>
   <si>
     <t>1003001,1003002,1003003,1003004,1003005,1003006,1003007,1003008,1003009,1003010,1003011,1003012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>json</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"a":"b","c":"d","e":"f"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -747,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="9" style="1"/>
@@ -761,7 +773,7 @@
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -831,8 +843,11 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -902,8 +917,11 @@
       <c r="W2" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="X2" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
@@ -971,7 +989,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
@@ -1026,8 +1044,11 @@
       <c r="S5" s="1">
         <v>1001</v>
       </c>
+      <c r="X5" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>1002</v>
       </c>
@@ -1083,7 +1104,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>1003</v>
       </c>
@@ -1142,7 +1163,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>2001</v>
       </c>
@@ -1174,7 +1195,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>2002</v>
       </c>
@@ -1203,7 +1224,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>2003</v>
       </c>
@@ -1232,7 +1253,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>2004</v>
       </c>
@@ -1261,7 +1282,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>2005</v>
       </c>

--- a/Excel/Role.xlsx
+++ b/Excel/Role.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747261B6-5138-4EDC-A064-DDC53675FC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338CF130-1BAA-4A94-BF57-4491C7A16075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -91,14 +91,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>attackWait</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>attackNextTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>weaponId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -143,10 +135,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>float[]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,14 +211,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>连击等待时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一击等待时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>武器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -279,14 +259,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.3,0.3,0.3,-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.15,0.15,0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Guy</t>
   </si>
   <si>
@@ -311,14 +283,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.6,0.6,0.6,-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.25,0.25,0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hagger</t>
   </si>
   <si>
@@ -343,10 +307,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.2,0.2,0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -404,18 +364,6 @@
   </si>
   <si>
     <t>1003001,1003002,1003003,1003004,1003005,1003006,1003007,1003008,1003009,1003010,1003011,1003012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>json</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"a":"b","c":"d","e":"f"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -759,21 +707,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="8" width="9" style="1"/>
-    <col min="9" max="11" width="9" style="2"/>
-    <col min="12" max="15" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="26.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="1"/>
     <col min="16" max="16" width="85.375" style="2" customWidth="1"/>
-    <col min="17" max="19" width="9" style="1"/>
-    <col min="20" max="20" width="9" style="2"/>
-    <col min="21" max="22" width="9" style="1"/>
-    <col min="23" max="23" width="9" style="2"/>
-    <col min="24" max="16384" width="9" style="1"/>
+    <col min="17" max="17" width="14.875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.875" style="2" customWidth="1"/>
+    <col min="19" max="20" width="9" style="1"/>
+    <col min="21" max="21" width="9" style="2"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -825,200 +784,176 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>101</v>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="2" t="s">
+    <row r="3" spans="1:21" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="W2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>102</v>
+      <c r="E3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H5" s="1">
         <v>0.7</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L5" s="1">
         <v>1001009</v>
@@ -1033,51 +968,42 @@
         <v>1001013</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" s="1">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="1">
         <v>1001</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>103</v>
-      </c>
     </row>
-    <row r="6" spans="1:24" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L6" s="1">
         <v>1002009</v>
@@ -1092,48 +1018,42 @@
         <v>1002013</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="S6" s="1">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="L7" s="1">
         <v>1003009</v>
@@ -1148,33 +1068,27 @@
         <v>1003012</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1003</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="R7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="S7" s="1">
-        <v>1003</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>83</v>
-      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>2001</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G8" s="1">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H8" s="1">
         <v>0.6</v>
@@ -1185,25 +1099,22 @@
       <c r="P8" s="2">
         <v>2001001</v>
       </c>
-      <c r="Q8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="U8" s="1">
+      <c r="S8" s="1">
         <v>2001</v>
       </c>
-      <c r="V8" s="1" t="s">
-        <v>86</v>
+      <c r="T8" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>2002</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G9" s="1">
         <v>0.5</v>
@@ -1217,25 +1128,22 @@
       <c r="P9" s="2">
         <v>2002001</v>
       </c>
-      <c r="Q9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="U9" s="1">
+      <c r="S9" s="1">
         <v>2002</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>2003</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="1">
         <v>0.5</v>
@@ -1246,25 +1154,22 @@
       <c r="P10" s="2">
         <v>2003001</v>
       </c>
-      <c r="Q10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="U10" s="1">
+      <c r="S10" s="1">
         <v>2003</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>2004</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="1">
         <v>0.5</v>
@@ -1273,55 +1178,50 @@
         <v>2004001</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="U11" s="1">
+        <v>83</v>
+      </c>
+      <c r="S11" s="1">
         <v>2004</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>2005</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>-1</v>
-      </c>
-      <c r="U12" s="1">
+        <v>89</v>
+      </c>
+      <c r="S12" s="1">
         <v>2005</v>
       </c>
-      <c r="W12" s="2" t="s">
-        <v>83</v>
+      <c r="U12" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/Role.xlsx
+++ b/Excel/Role.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338CF130-1BAA-4A94-BF57-4491C7A16075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F45FDEE-A9F0-4052-84F8-19ECAE4B59DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -234,15 +234,6 @@
     <t>Cody</t>
   </si>
   <si>
-    <t>Character/Cody</t>
-  </si>
-  <si>
-    <t>CodyHit</t>
-  </si>
-  <si>
-    <t>Icon/Character/Cody</t>
-  </si>
-  <si>
     <t>40,140</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -262,15 +253,6 @@
     <t>Guy</t>
   </si>
   <si>
-    <t>Character/Guy</t>
-  </si>
-  <si>
-    <t>GuyHit</t>
-  </si>
-  <si>
-    <t>Icon/Character/Guy</t>
-  </si>
-  <si>
     <t>1002001,1002002,1002003,1002004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -286,15 +268,6 @@
     <t>Hagger</t>
   </si>
   <si>
-    <t>Character/Hagger</t>
-  </si>
-  <si>
-    <t>HaggerHit</t>
-  </si>
-  <si>
-    <t>Icon/Character/Hagger</t>
-  </si>
-  <si>
     <t>40,160</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -314,9 +287,6 @@
     <t>Bred</t>
   </si>
   <si>
-    <t>Character/Bred</t>
-  </si>
-  <si>
     <t>Hurt1,Hurt2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -324,21 +294,12 @@
     <t>TwoP</t>
   </si>
   <si>
-    <t>Character/TwoP</t>
-  </si>
-  <si>
     <t>Axl</t>
   </si>
   <si>
-    <t>Character/Axl</t>
-  </si>
-  <si>
     <t>Andore</t>
   </si>
   <si>
-    <t>Character/Andore</t>
-  </si>
-  <si>
     <t>2004001,2004002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -346,9 +307,6 @@
     <t>Damnd</t>
   </si>
   <si>
-    <t>Character/Damnd</t>
-  </si>
-  <si>
     <t>80,160</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -364,6 +322,62 @@
   </si>
   <si>
     <t>1003001,1003002,1003003,1003004,1003005,1003006,1003007,1003008,1003009,1003010,1003011,1003012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Cody.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Guy.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Hagger.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Bred.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/TwoP.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Axl.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Andore.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/Damnd.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CodyHit.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuyHit.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HaggerHit.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common/Cody.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commonr/Guy.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common/Hagger.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -932,13 +946,13 @@
         <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="G5" s="1">
         <v>0.2</v>
@@ -947,13 +961,13 @@
         <v>0.7</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L5" s="1">
         <v>1001009</v>
@@ -968,7 +982,7 @@
         <v>1001013</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="1">
         <v>1001</v>
@@ -979,16 +993,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="G6" s="1">
         <v>0.3</v>
@@ -997,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L6" s="1">
         <v>1002009</v>
@@ -1018,7 +1032,7 @@
         <v>1002013</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="Q6" s="1">
         <v>1002</v>
@@ -1029,16 +1043,16 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="G7" s="1">
         <v>0.1</v>
@@ -1047,13 +1061,13 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L7" s="1">
         <v>1003009</v>
@@ -1068,13 +1082,13 @@
         <v>1003012</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="1">
         <v>1003</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
@@ -1082,10 +1096,10 @@
         <v>2001</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8" s="1">
         <v>0.1</v>
@@ -1103,7 +1117,7 @@
         <v>2001</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
@@ -1111,10 +1125,10 @@
         <v>2002</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G9" s="1">
         <v>0.5</v>
@@ -1137,10 +1151,10 @@
         <v>2003</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G10" s="1">
         <v>0.2</v>
@@ -1163,10 +1177,10 @@
         <v>2004</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="1">
         <v>0.2</v>
@@ -1178,7 +1192,7 @@
         <v>2004001</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="S11" s="1">
         <v>2004</v>
@@ -1189,10 +1203,10 @@
         <v>2005</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="G12" s="1">
         <v>0.5</v>
@@ -1201,22 +1215,22 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="S12" s="1">
         <v>2005</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Role.xlsx
+++ b/Excel/Role.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F45FDEE-A9F0-4052-84F8-19ECAE4B59DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C74A5A-1250-475F-B195-B518D15CA148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -938,7 +938,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>

--- a/Excel/Role.xlsx
+++ b/Excel/Role.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C74A5A-1250-475F-B195-B518D15CA148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A81B68-9DA8-4A4D-B384-A57DFF8ABFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Role" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
